--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.29535759922913</v>
+        <v>6.060495609874733</v>
       </c>
       <c r="D2" t="n">
-        <v>37.35291020263829</v>
+        <v>6.069847907928723</v>
       </c>
       <c r="E2" t="n">
-        <v>5.177194563318886</v>
+        <v>0.841294116539319</v>
       </c>
       <c r="F2" t="n">
-        <v>5.19260177217941</v>
+        <v>0.8437977879791541</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.84685326993105</v>
+        <v>3.550113656363796</v>
       </c>
       <c r="D3" t="n">
-        <v>21.87612892799458</v>
+        <v>3.554870950799119</v>
       </c>
       <c r="E3" t="n">
-        <v>5.177194563318886</v>
+        <v>0.841294116539319</v>
       </c>
       <c r="F3" t="n">
-        <v>5.19260177217941</v>
+        <v>0.8437977879791541</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.31910751873346</v>
+        <v>3.626854971794188</v>
       </c>
       <c r="D4" t="n">
-        <v>22.31423345997914</v>
+        <v>3.62606293724661</v>
       </c>
       <c r="E4" t="n">
-        <v>5.177194563318886</v>
+        <v>0.841294116539319</v>
       </c>
       <c r="F4" t="n">
-        <v>5.19260177217941</v>
+        <v>0.8437977879791541</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.55952062875658</v>
+        <v>5.128422102172945</v>
       </c>
       <c r="D5" t="n">
-        <v>31.52086961809288</v>
+        <v>5.122141312940094</v>
       </c>
       <c r="E5" t="n">
-        <v>5.177194563318886</v>
+        <v>0.841294116539319</v>
       </c>
       <c r="F5" t="n">
-        <v>5.19260177217941</v>
+        <v>0.8437977879791541</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.41471912806181</v>
+        <v>3.967391858310044</v>
       </c>
       <c r="D6" t="n">
-        <v>24.36814361822146</v>
+        <v>3.959823337960987</v>
       </c>
       <c r="E6" t="n">
-        <v>5.177194563318886</v>
+        <v>0.841294116539319</v>
       </c>
       <c r="F6" t="n">
-        <v>5.19260177217941</v>
+        <v>0.8437977879791541</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.88531160776963</v>
+        <v>4.043863136262565</v>
       </c>
       <c r="D7" t="n">
-        <v>24.83957728055846</v>
+        <v>4.036431308090751</v>
       </c>
       <c r="E7" t="n">
-        <v>5.177194563318886</v>
+        <v>0.841294116539319</v>
       </c>
       <c r="F7" t="n">
-        <v>5.19260177217941</v>
+        <v>0.8437977879791541</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.85279676758734</v>
+        <v>4.201079474732942</v>
       </c>
       <c r="D8" t="n">
-        <v>25.80033459488769</v>
+        <v>4.192554371669249</v>
       </c>
       <c r="E8" t="n">
-        <v>5.177194563318886</v>
+        <v>0.841294116539319</v>
       </c>
       <c r="F8" t="n">
-        <v>5.19260177217941</v>
+        <v>0.8437977879791541</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
